--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486851_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486851_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>13.3164</v>
+        <v>11.9087</v>
       </c>
       <c r="E2" t="n">
-        <v>12.5951</v>
+        <v>11.1578</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7213000000000001</v>
+        <v>0.7509</v>
       </c>
       <c r="G2" t="n">
         <v>1.3127</v>
@@ -610,13 +610,13 @@
         <v>2.6694</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6116</v>
+        <v>1.2039</v>
       </c>
       <c r="T2" t="n">
-        <v>2.177</v>
+        <v>0.7397</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4345</v>
+        <v>0.4641</v>
       </c>
       <c r="V2" t="n">
         <v>6.7227</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5848</v>
+        <v>1.8064</v>
       </c>
       <c r="E3" t="n">
-        <v>1.355</v>
+        <v>0.7546</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2297</v>
+        <v>1.0519</v>
       </c>
       <c r="G3" t="n">
         <v>3.2435</v>
@@ -688,13 +688,13 @@
         <v>1.6427</v>
       </c>
       <c r="S3" t="n">
-        <v>1.377</v>
+        <v>0.5986</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8405</v>
+        <v>0.24</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5365</v>
+        <v>0.3586</v>
       </c>
       <c r="V3" t="n">
         <v>-0.5983000000000001</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5571</v>
+        <v>1.4731</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3963</v>
+        <v>1.2529</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1609</v>
+        <v>0.2202</v>
       </c>
       <c r="G4" t="n">
         <v>2.3643</v>
@@ -766,13 +766,13 @@
         <v>1.0267</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0999</v>
+        <v>-0.184</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0931</v>
+        <v>-0.2364</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0068</v>
+        <v>0.0524</v>
       </c>
       <c r="V4" t="n">
         <v>-0.7072000000000001</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. MERLO</t>
+          <t>B. VANACLOCHA SANCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5972</v>
+        <v>1.4059</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.6039</v>
+        <v>-0.3205</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2011</v>
+        <v>1.7264</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7291</v>
+        <v>1.2152</v>
       </c>
       <c r="H5" t="n">
-        <v>2.073</v>
+        <v>1.3726</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.8021</v>
+        <v>-0.1575</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8643</v>
+        <v>1.8222</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9038</v>
+        <v>1.7038</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.0396</v>
+        <v>0.1184</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5933</v>
+        <v>-0.607</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8308</v>
+        <v>-0.3311</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7625</v>
+        <v>-0.2759</v>
       </c>
       <c r="P5" t="n">
-        <v>0.616</v>
+        <v>0.4107</v>
       </c>
       <c r="Q5" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R5" t="n">
-        <v>2.6694</v>
+        <v>2.4641</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7103</v>
+        <v>0.0203</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4147</v>
+        <v>-0.0892</v>
       </c>
       <c r="U5" t="n">
-        <v>1.125</v>
+        <v>0.1096</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. VANACLOCHA SANCHEZ</t>
+          <t>S. MERLO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5049</v>
+        <v>0.473</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.014</v>
+        <v>-1.2242</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5189</v>
+        <v>1.6972</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2152</v>
+        <v>-0.7291</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3726</v>
+        <v>2.073</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1575</v>
+        <v>-2.8021</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8222</v>
+        <v>0.8643</v>
       </c>
       <c r="K6" t="n">
-        <v>1.7038</v>
+        <v>2.9038</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1184</v>
+        <v>-2.0396</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.607</v>
+        <v>-1.5933</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3311</v>
+        <v>-0.8308</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2759</v>
+        <v>-0.7625</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4107</v>
+        <v>0.616</v>
       </c>
       <c r="Q6" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4641</v>
+        <v>2.6694</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8807</v>
+        <v>0.586</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7827</v>
+        <v>-0.0351</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0979</v>
+        <v>0.6211</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. PEREZ CONTI</t>
+          <t>J. GONZALEZ ALBADALEJO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.3597</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0659</v>
+        <v>-2.4001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1345</v>
+        <v>2.7598</v>
       </c>
       <c r="G7" t="n">
-        <v>0.308</v>
+        <v>-3.9255</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1104</v>
+        <v>-2.0204</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4184</v>
+        <v>-1.9051</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-3.3422</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-1.8287</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-1.5135</v>
       </c>
       <c r="M7" t="n">
-        <v>0.308</v>
+        <v>-0.5833</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1104</v>
+        <v>-0.1917</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4184</v>
+        <v>-0.3916</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2053</v>
+        <v>3.0801</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2053</v>
+        <v>3.0801</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4448</v>
+        <v>0.1443</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0659</v>
+        <v>-0.2365</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3789</v>
+        <v>0.3808</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.0608</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.1179</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. VERA PICAZO</t>
+          <t>A. PEREZ CONTI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,31 +1033,31 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.242</v>
+        <v>0.2325</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9878</v>
+        <v>0.0387</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7458</v>
+        <v>0.1938</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3504</v>
+        <v>0.308</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.07140000000000001</v>
+        <v>-0.1104</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2789</v>
+        <v>0.4184</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6584</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0389</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6974</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0.308</v>
@@ -1069,37 +1069,37 @@
         <v>0.4184</v>
       </c>
       <c r="P8" t="n">
-        <v>0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3898</v>
+        <v>-0.2809</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3294</v>
+        <v>0.0387</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0604</v>
+        <v>-0.3196</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1179</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1179</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. GONZALEZ ALBADALEJO</t>
+          <t>A. VERA PICAZO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1581</v>
+        <v>-0.1234</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.4733</v>
+        <v>-0.9878</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3152</v>
+        <v>0.8643</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.9255</v>
+        <v>-0.3504</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.0204</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.9051</v>
+        <v>-0.2789</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.3422</v>
+        <v>-0.6584</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.8287</v>
+        <v>0.0389</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.5135</v>
+        <v>-0.6974</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5833</v>
+        <v>0.308</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1917</v>
+        <v>-0.1104</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3916</v>
+        <v>0.4184</v>
       </c>
       <c r="P9" t="n">
-        <v>3.0801</v>
+        <v>0.616</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.0801</v>
+        <v>0.616</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3736</v>
+        <v>-0.2712</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.3097</v>
+        <v>-0.3294</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0638</v>
+        <v>0.0581</v>
       </c>
       <c r="V9" t="n">
-        <v>1.0608</v>
+        <v>-0.1179</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>-0.1179</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3213</v>
+        <v>-2.0528</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8558</v>
+        <v>-1.6466</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4655</v>
+        <v>-0.4062</v>
       </c>
       <c r="G10" t="n">
         <v>-0.784</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5106000000000001</v>
+        <v>-0.2421</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1317</v>
+        <v>0.0775</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3789</v>
+        <v>-0.3196</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4274</v>
+        <v>-2.1523</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1325</v>
+        <v>-1.8574</v>
       </c>
       <c r="F11" t="n">
         <v>-0.2949</v>
@@ -1312,10 +1312,10 @@
         <v>0.8214</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1549</v>
+        <v>0.1202</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4534</v>
+        <v>-0.1783</v>
       </c>
       <c r="U11" t="n">
         <v>0.2985</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7365</v>
+        <v>-4.9283</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.656</v>
+        <v>-3.5514</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0805</v>
+        <v>-1.3769</v>
       </c>
       <c r="G12" t="n">
         <v>-5.9437</v>
@@ -1390,13 +1390,13 @@
         <v>1.2321</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1472</v>
+        <v>-0.339</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2907</v>
+        <v>-0.1861</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1435</v>
+        <v>-0.1529</v>
       </c>
       <c r="V12" t="n">
         <v>0.1224</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.743699999999998</v>
+        <v>8.402500000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5572000000000004</v>
+        <v>1.215999999999999</v>
       </c>
       <c r="F13" t="n">
         <v>7.1865</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.329399999999999</v>
+        <v>-4.3294</v>
       </c>
       <c r="H13" t="n">
         <v>4.023700000000001</v>
@@ -1441,16 +1441,16 @@
         <v>-8.353</v>
       </c>
       <c r="J13" t="n">
-        <v>3.384800000000001</v>
+        <v>3.384799999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>9.557399999999999</v>
+        <v>9.557400000000001</v>
       </c>
       <c r="L13" t="n">
         <v>-6.172800000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-7.714099999999999</v>
+        <v>-7.7141</v>
       </c>
       <c r="N13" t="n">
         <v>-5.533799999999999</v>
@@ -1468,13 +1468,13 @@
         <v>16.4272</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6974000000000004</v>
+        <v>1.3561</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8537999999999999</v>
+        <v>-0.1951</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5513</v>
+        <v>1.5511</v>
       </c>
       <c r="V13" t="n">
         <v>6.242299999999999</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. MIKHAILOV PALTARAK</t>
+          <t>J. CARRASCO MARTIN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0788</v>
+        <v>2.0774</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0711</v>
+        <v>1.1819</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0077</v>
+        <v>0.8956</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9782999999999999</v>
+        <v>3.9448</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0492</v>
+        <v>2.316</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9292</v>
+        <v>1.6288</v>
       </c>
       <c r="J14" t="n">
-        <v>1.6559</v>
+        <v>4.7619</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3797</v>
+        <v>3.3676</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2763</v>
+        <v>1.3943</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6776</v>
+        <v>-0.8171</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.3305</v>
+        <v>-1.0516</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6529</v>
+        <v>0.2345</v>
       </c>
       <c r="P14" t="n">
         <v>-1.8481</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.2855</v>
+        <v>-3.0801</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4374</v>
+        <v>1.2321</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2279</v>
+        <v>-0.0193</v>
       </c>
       <c r="T14" t="n">
-        <v>0.98</v>
+        <v>-0.4999</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2479</v>
+        <v>0.4806</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7207</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7207</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. CARRASCO MARTIN</t>
+          <t>J. GOLSON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9659</v>
+        <v>1.5937</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9726</v>
+        <v>1.355</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9933</v>
+        <v>0.2388</v>
       </c>
       <c r="G15" t="n">
-        <v>3.9448</v>
+        <v>1.5637</v>
       </c>
       <c r="H15" t="n">
-        <v>2.316</v>
+        <v>-1.4567</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6288</v>
+        <v>3.0205</v>
       </c>
       <c r="J15" t="n">
-        <v>4.7619</v>
+        <v>1.734</v>
       </c>
       <c r="K15" t="n">
-        <v>3.3676</v>
+        <v>-0.5416</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3943</v>
+        <v>2.2756</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8171</v>
+        <v>-0.1702</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0516</v>
+        <v>-0.9151</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2345</v>
+        <v>0.7449</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.8481</v>
+        <v>0.2053</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.0801</v>
+        <v>-1.2321</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1309</v>
+        <v>-0.1754</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7091</v>
+        <v>-0.3256</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5783</v>
+        <v>0.1502</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1849</v>
+        <v>1.2738</v>
       </c>
       <c r="E16" t="n">
         <v>0.4912</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6937</v>
+        <v>0.7826</v>
       </c>
       <c r="G16" t="n">
         <v>0.8467</v>
@@ -1702,13 +1702,13 @@
         <v>0.4107</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0725</v>
+        <v>0.0165</v>
       </c>
       <c r="T16" t="n">
         <v>-0.1317</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0593</v>
+        <v>0.1482</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. GOLSON</t>
+          <t>B. ALVAREZ TORRES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.783</v>
+        <v>0.4146</v>
       </c>
       <c r="E17" t="n">
-        <v>0.832</v>
+        <v>0.6374</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0489</v>
+        <v>-0.2228</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5637</v>
+        <v>1.7927</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.4567</v>
+        <v>-0.12</v>
       </c>
       <c r="I17" t="n">
-        <v>3.0205</v>
+        <v>1.9128</v>
       </c>
       <c r="J17" t="n">
-        <v>1.734</v>
+        <v>1.9316</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5416</v>
+        <v>0.8794</v>
       </c>
       <c r="L17" t="n">
-        <v>2.2756</v>
+        <v>1.0522</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1702</v>
+        <v>-0.1388</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9151</v>
+        <v>-0.9994</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7449</v>
+        <v>0.8606</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2053</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.2321</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4374</v>
+        <v>1.0267</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.986</v>
+        <v>0.0058</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8486</v>
+        <v>-0.0621</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1374</v>
+        <v>0.0679</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>-1.1786</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. SALA VALLMAJO</t>
+          <t>M. MIKHAILOV PALTARAK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.051</v>
+        <v>0.3876</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7243000000000001</v>
+        <v>-0.8703</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7753</v>
+        <v>1.2579</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.2163</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6584</v>
+        <v>0.0492</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5579</v>
+        <v>0.9292</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.3558</v>
+        <v>1.6559</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6584</v>
+        <v>1.3797</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6974</v>
+        <v>0.2763</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1395</v>
+        <v>-0.6776</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-1.3305</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1395</v>
+        <v>0.6529</v>
       </c>
       <c r="P18" t="n">
-        <v>0.616</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.2855</v>
       </c>
       <c r="R18" t="n">
-        <v>0.616</v>
+        <v>1.4374</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6512</v>
+        <v>0.5366</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6315</v>
+        <v>0.0385</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0198</v>
+        <v>0.4981</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.7207</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.7207</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. ALVAREZ TORRES</t>
+          <t>P. SALA VALLMAJO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0492</v>
+        <v>-0.1286</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1144</v>
+        <v>-0.9335</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1635</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>1.7927</v>
+        <v>-1.2163</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.12</v>
+        <v>-0.6584</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9128</v>
+        <v>-0.5579</v>
       </c>
       <c r="J19" t="n">
-        <v>1.9316</v>
+        <v>-1.3558</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8794</v>
+        <v>-0.6584</v>
       </c>
       <c r="L19" t="n">
-        <v>1.0522</v>
+        <v>-0.6974</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1388</v>
+        <v>0.1395</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9994</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8606</v>
+        <v>0.1395</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2053</v>
+        <v>0.616</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.2321</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0267</v>
+        <v>0.616</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4579</v>
+        <v>0.4717</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5851</v>
+        <v>0.4223</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1272</v>
+        <v>0.0494</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5449000000000001</v>
+        <v>-0.9772</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6788999999999999</v>
+        <v>-0.9927</v>
       </c>
       <c r="F20" t="n">
-        <v>0.134</v>
+        <v>0.0155</v>
       </c>
       <c r="G20" t="n">
         <v>0.8398</v>
@@ -2014,13 +2014,13 @@
         <v>0.8214</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8741</v>
+        <v>0.4417</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3834</v>
+        <v>0.0696</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4906</v>
+        <v>0.3721</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. VALERA COROMINAS</t>
+          <t>N. OKEKE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1502</v>
+        <v>-1.6052</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9261</v>
+        <v>0.2937</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2241</v>
+        <v>-1.8989</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0336</v>
+        <v>1.4658</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1427</v>
+        <v>-0.4385</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1763</v>
+        <v>1.9043</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0775</v>
+        <v>2.1458</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6069</v>
+        <v>0.7786</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6843</v>
+        <v>1.3672</v>
       </c>
       <c r="M21" t="n">
-        <v>0.111</v>
+        <v>-0.68</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-1.2171</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8606</v>
+        <v>0.5372</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.2053</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0267</v>
+        <v>-1.2321</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0267</v>
+        <v>1.4374</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1756</v>
+        <v>-0.9192</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1781</v>
+        <v>-0.6201</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3537</v>
+        <v>-0.2991</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.0082</v>
+        <v>-2.3573</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.0082</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. OKEKE</t>
+          <t>I. VALERA COROMINAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4299</v>
+        <v>-2.0124</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1248</v>
+        <v>-1.1353</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3051</v>
+        <v>-0.8771</v>
       </c>
       <c r="G22" t="n">
-        <v>1.4658</v>
+        <v>0.0336</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4385</v>
+        <v>-0.1427</v>
       </c>
       <c r="I22" t="n">
-        <v>1.9043</v>
+        <v>0.1763</v>
       </c>
       <c r="J22" t="n">
-        <v>2.1458</v>
+        <v>-0.0775</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7786</v>
+        <v>0.6069</v>
       </c>
       <c r="L22" t="n">
-        <v>1.3672</v>
+        <v>-0.6843</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.68</v>
+        <v>0.111</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2171</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5372</v>
+        <v>0.8606</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2053</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.2321</v>
+        <v>-1.0267</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4374</v>
+        <v>1.0267</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7438</v>
+        <v>-0.0378</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0385</v>
+        <v>-0.0311</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7053</v>
+        <v>-0.0067</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.3573</v>
+        <v>-2.0082</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.3573</v>
+        <v>-2.0082</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1833</v>
+        <v>-3.6497</v>
       </c>
       <c r="E23" t="n">
         <v>-4.4151</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2318</v>
+        <v>0.7653</v>
       </c>
       <c r="G23" t="n">
         <v>-3.4192</v>
@@ -2248,13 +2248,13 @@
         <v>1.0267</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7641</v>
+        <v>-0.2306</v>
       </c>
       <c r="T23" t="n">
         <v>-0.3334</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4307</v>
+        <v>0.1029</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.45</v>
+        <v>-4.4204</v>
       </c>
       <c r="E24" t="n">
         <v>-2.7987</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6513</v>
+        <v>-1.6216</v>
       </c>
       <c r="G24" t="n">
         <v>-2.5007</v>
@@ -2326,13 +2326,13 @@
         <v>0.8214</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1197</v>
+        <v>-0.0901</v>
       </c>
       <c r="T24" t="n">
         <v>-0.07770000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0421</v>
+        <v>-0.0124</v>
       </c>
       <c r="V24" t="n">
         <v>-1.4189</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.7439</v>
+        <v>-7.046399999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.186599999999999</v>
+        <v>-7.186399999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.5570999999999999</v>
+        <v>0.1402000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>4.3292</v>
@@ -2380,7 +2380,7 @@
         <v>7.714099999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>5.533799999999999</v>
+        <v>5.5338</v>
       </c>
       <c r="L25" t="n">
         <v>2.1804</v>
@@ -2389,10 +2389,10 @@
         <v>-3.3846</v>
       </c>
       <c r="N25" t="n">
-        <v>-9.557399999999999</v>
+        <v>-9.557400000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>6.172800000000001</v>
+        <v>6.1728</v>
       </c>
       <c r="P25" t="n">
         <v>-5.1337</v>
@@ -2404,13 +2404,13 @@
         <v>11.2939</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6973000000000001</v>
+        <v>-0.0001000000000000584</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.5511</v>
+        <v>-1.5512</v>
       </c>
       <c r="U25" t="n">
-        <v>0.8538999999999999</v>
+        <v>1.5512</v>
       </c>
       <c r="V25" t="n">
         <v>-6.242299999999999</v>
